--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_11_Guardrails _ AI Safety/Day_11_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_11_Guardrails _ AI Safety/Day_11_Phan_02_22_Cau.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>60</v>
@@ -639,7 +639,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không có verdict khác với verdict benign.</t>
+          <t>Kết luận 'An toàn vì ít nhất một detector đã cho qua' là sai lầm nguy hiểm; trong mô hình phòng thủ nhiều lớp, khi learned detector bị timeout thì hệ thống rơi vào trạng thái không xác định và phải xử lý fail-closed hoặc chuyển duyệt tùy mức rủi ro.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -687,7 +687,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ngoài phạm vi không đồng nghĩa tấn công.</t>
+          <t>Người dùng hỏi 'quy trình nghỉ phép' nằm đúng trong phạm vi phúc lợi nhân viên; hệ thống phải đánh giá dựa trên ý định ngữ nghĩa (semantic intent) chứ không được chặn máy móc vì thiếu từ khóa 'phúc lợi'.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -735,7 +735,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Evict timestamp cũ nhất khi nó ra khỏi 60 giây.</t>
+          <t>Cửa sổ trượt 60s cho tối đa 3 requests. Các mốc hiện tại: t=0, 20, 40s. Sự kiện tại t=0 chỉ bị loại khi t_event &lt;= now - 60 =&gt; now &gt;= 60s. Tại thời điểm hiện tại now=50s, cần thêm tối thiểu 60 - 50 = 10 giây để request cũ nhất được evict khỏi cửa sổ trượt.</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3</t>
+          <t>o2 → o3 → o1</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -786,7 +786,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bước cuối chỉ xuất hiện trên pass path.</t>
+          <t>Nhánh xử lý khi bị chặn: Parse/trích xuất text đầu vào của người dùng (o2) → chạy chuỗi guardrails kiểm tra theo thứ tự (o3) → trả phản hồi bị chặn và ghi log lý do kiểm toán (o1).</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>60</v>
@@ -834,7 +834,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ai tạo dấu phân cách, và model hoặc hệ khi vận hành có thực thi vai trò đó không?</t>
+          <t>Để ngăn chặn tấn công giả mạo dấu phân cách (delimiter injection), giải pháp bền vững là sử dụng cấu trúc dữ liệu có kiểu rõ ràng (typed structured channels) kèm escaping phù hợp, coi toàn bộ tài liệu là dữ liệu thuần túy.</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -882,7 +882,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt finding với hành động xử lý finding.</t>
+          <t>Bộ phát hiện rò rỉ dữ liệu phải nhận diện và gắn thẻ cụ thể theo từng loại và vị trí dữ liệu nhạy cảm (email, API key bí mật, mã đơn công khai) để hệ thống phía sau quyết định hành động tương ứng.</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -930,7 +930,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Policy quyết định che hay chặn dựa trên loại phát hiện và khả năng giữ phần nội dung còn hữu ích.</t>
+          <t>Khi chính sách cho phép che dữ liệu (redaction), quy trình đúng là che thông tin nhạy cảm, quét lại một lần nữa để xác nhận an toàn, rồi mới phát hành nội dung hữu ích còn lại.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60</v>
@@ -978,7 +978,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng dùng kết quả đạt của một cổng chất lượng để thay cho kết luận an toàn ở cổng khác.</t>
+          <t>Chính sách an toàn nội dung hoạt động độc lập với tính đầy đủ hay định dạng; ngay cả khi đầu ra có trích dẫn đúng và chuẩn schema, nếu chứa hướng dẫn thuộc nhóm bị cấm thì vẫn bắt buộc phải bị chặn.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1026,7 +1026,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Judge phải biết đánh giá theo rule nào và phải trả theo contract nào.</t>
+          <t>Lỗ hổng thiết kế của LLM judge trong tình huống này là rubric thiếu schema định nghĩa phân loại/kết luận rõ ràng, đồng thời cấp thừa ngữ cảnh (lộ cả system prompt bí mật) cho bộ đánh giá.</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1074,7 +1074,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách collection của findings khỏi final action.</t>
+          <t>Khi có xung đột giữa các chính sách (PII yêu cầu che nhưng moderation yêu cầu chặn), hành động chặn an toàn có độ ưu tiên cao nhất, đồng thời phải lưu giữ đầy đủ các phát hiện phục vụ kiểm toán.</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Artifact được đánh giá trước và sau transform có cùng content hash không?</t>
+          <t>Văn bản sau khi che PII đã trở thành một artifact mới; các cổng kiểm tra an toàn và hợp đồng dữ liệu liên quan phải được chạy lại trên văn bản mới trước khi phát hành ra ngoài.</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1216,7 +1216,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một nơi hợp lệ không làm mọi dữ liệu gửi tới đó hợp lệ.</t>
+          <t>Quy tắc kiểm soát luồng dữ liệu ra ngoài (egress control): Đích đến nằm trong allowlist không đồng nghĩa được gửi mọi thứ; nếu nội dung chứa access token không cần thiết thì phải chặn không gửi.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1264,7 +1264,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lời đồng ý mơ hồ không đủ liên kết với action cụ thể.</t>
+          <t>Thao tác tài chính giá trị lớn (80 triệu) có rủi ro rất cao; khi không có mã định danh người duyệt hay chữ ký số hợp lệ trong nhật ký, hệ thống bắt buộc phải dừng thực thi (fail closed).</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1319,7 +1319,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng chỉ đếm thành phần; kiểm tra xem chúng có nằm trên cùng một đường dẫn không.</t>
+          <t>Mô hình 'Lethal Trifecta' trong bảo mật agentic LLM (Simon Willison) bao gồm đúng ba thành phần trên cùng một luồng dữ liệu: (a) Tiếp nhận nội dung không đáng tin cậy từ bên ngoài (email); (b) Truy cập dữ liệu nhạy cảm nội bộ (CRM); (c) Có công cụ giao tiếp/hành động ra bên ngoài (POST ra Internet).</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1367,7 +1367,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So quyền thực tế của reader và executor, không chỉ so tên gọi.</t>
+          <t>Reader không phải là môi trường cách ly (quarantine) thực sự nếu nó vẫn giữ quyền truy cập CRM và gọi công cụ gửi email; dữ liệu lạ vẫn có thể bị lợi dụng để tấn công vào hệ thống nội bộ.</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1415,7 +1415,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kết quả tool có quyền chọn action mới không?</t>
+          <t>Selector đã chọn cố định hành động `lookup_order`; kết quả trả về từ công cụ chỉ được xem là dữ liệu và tuyệt đối không được phép tự ý thay đổi hoặc bổ sung hành động mới (`refund_all`).</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1514,7 +1514,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ordering dependency có thể là một safety invariant.</t>
+          <t>Thứ tự thực thi các bước (ordering dependency) thường là một bất biến an toàn; việc đổi thứ tự cấu thành thay đổi plan và bắt buộc phải qua quy trình phê duyệt lại.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1562,7 +1562,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi mapper được thấy bao nhiêu tài liệu?</t>
+          <t>Để ngăn chặn cross-document prompt injection giữa các tài liệu cạnh tranh, kiến trúc chuẩn là cô lập từng tài liệu trong một mapper riêng biệt, sau đó dùng reducer phi-LLM (deterministic) để tổng hợp kết quả có cấu trúc.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dữ liệu có được phép thay đổi luồng điều khiển hoặc quyền không?</t>
+          <t>Khi xử lý tệp CSV từ bên ngoài, giải pháp an toàn là cố định logic mã nguồn từ schema đáng tin cậy và xử lý dữ liệu CSV trong môi trường sandbox được cô lập, không cho phép mô hình sinh mã động dựa trên nội dung tệp.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>60</v>
@@ -1658,7 +1658,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Executor thật sự cần field nào để chạy bước đã được chốt?</t>
+          <t>Nguyên tắc đặc quyền tối thiểu (Least Privilege Context): Executor chỉ cần nhận `order_id`, action đã được chốt và các trường dữ liệu cần thiết để thực thi, không được chuyển toàn bộ lịch sử chat chứa mật khẩu và nội dung web không an toàn.</t>
         </is>
       </c>
     </row>
